--- a/02_DIA_inicio_2026_analisis_assets/rbd_9625_escuela-basica-villa-la-cultura_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9625_escuela-basica-villa-la-cultura_nt2_rubricas.xlsx
@@ -1848,13 +1848,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D71B1596-8C17-4E7D-B7EC-2DDBE177F1BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C1F312-C15B-4262-8AF8-51D912B9F733}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24E9072F-FE06-409D-B9B6-72C2DFD1FDB0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E042DB9A-A5D7-4AE9-97C5-D6D627998E99}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7EE3B6E-B42A-421B-B680-9E6ACDD10C00}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA8C0883-A340-40E3-A4C2-6D8C22F311BE}"/>
 </file>